--- a/Fearnleys/Fearnleys_USG_Positions_All_Emails.xlsx
+++ b/Fearnleys/Fearnleys_USG_Positions_All_Emails.xlsx
@@ -205,7 +205,7 @@
     <t>sub Pan</t>
   </si>
   <si>
-    <t>2026-02-27 16:01:35</t>
+    <t>2026-02-24</t>
   </si>
   <si>
     <t>C:\Users\THADLOW\OneDrive - Axpo Services AG\Desktop\SHIPPING BROKER REPORTS\Fearnleys\Emails\2026-02-27_160137__FW_ FEARNLEYS VLGC MORNING REPORT 24 FEB 2026\2026-02-27_160137__FW_ FEARNLEYS VLGC MORNING REPORT 24 FEB 2026.msg</t>
